--- a/data/trans_camb/P1419-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1419-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; -0,59</t>
+          <t>-2,95; -0,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,6</t>
+          <t>-2,85; -0,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,3</t>
+          <t>-1,73; 3,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; -0,25</t>
+          <t>-1,46; -0,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; -0,29</t>
+          <t>-1,51; -0,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,34</t>
+          <t>-0,8; 1,34</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,04%</t>
+          <t>-6,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-11,51%</t>
+          <t>-9,72%</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 1034,94</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 498,28</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,71</t>
+          <t>-3,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,96</t>
+          <t>-1,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,12</t>
+          <t>-1,93; 0,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; -0,09</t>
+          <t>-2,08; -0,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,51</t>
+          <t>-1,81; 0,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -1,81</t>
+          <t>-5,96; -1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -2,41</t>
+          <t>-6,29; -2,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; -1,82</t>
+          <t>-5,38; -1,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -1,09</t>
+          <t>-3,38; -1,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; -1,59</t>
+          <t>-3,59; -1,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -0,85</t>
+          <t>-2,91; -0,41</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-51,28%</t>
+          <t>-54,9%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-75,05%</t>
+          <t>-61,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-67,92%</t>
+          <t>-57,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-92,95; 53,1</t>
+          <t>-100,0; 58,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 157,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 136,34</t>
+          <t>-100,0; 125,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-91,32; -45,61</t>
+          <t>-91,39; -49,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-96,65; -63,8</t>
+          <t>-96,49; -61,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,44; -40,78</t>
+          <t>-83,21; -19,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,71; -48,07</t>
+          <t>-87,82; -45,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-95,54; -63,79</t>
+          <t>-95,23; -63,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-86,94; -31,38</t>
+          <t>-81,17; -17,06</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,2</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,7</t>
+          <t>-2,0; 0,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; -0,43</t>
+          <t>-2,61; -0,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,29</t>
+          <t>-0,82; 2,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 1,16</t>
+          <t>-4,28; 1,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -3,41</t>
+          <t>-7,79; -3,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,46</t>
+          <t>-3,79; 1,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,31</t>
+          <t>-2,88; 0,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; -2,38</t>
+          <t>-4,88; -2,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,13</t>
+          <t>-1,86; 1,19</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-16,4%</t>
+          <t>-13,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-10,09%</t>
+          <t>-7,58%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-87,51; 114,88</t>
+          <t>-88,5; 107,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,64</t>
+          <t>-100,0; 11,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,6; 244,04</t>
+          <t>-41,59; 214,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 20,92</t>
+          <t>-49,8; 19,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,87; -53,55</t>
+          <t>-86,7; -51,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 25,67</t>
+          <t>-42,35; 23,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,12; 10,85</t>
+          <t>-54,62; 6,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-87,47; -60,86</t>
+          <t>-87,93; -59,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-37,66; 30,43</t>
+          <t>-34,24; 33,1</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; -0,36</t>
+          <t>-4,52; -0,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,03</t>
+          <t>-3,51; 0,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,89</t>
+          <t>-2,81; 1,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,6; -0,6</t>
+          <t>-7,29; -0,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,22; -1,59</t>
+          <t>-8,17; -1,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,98</t>
+          <t>-1,55; 4,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -1,15</t>
+          <t>-5,31; -1,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; -1,16</t>
+          <t>-5,18; -1,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,89</t>
+          <t>-1,08; 2,91</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-34,08%</t>
+          <t>-6,65%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-5,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,15; -0,6</t>
+          <t>-84,74; -9,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 39,31</t>
+          <t>-66,29; 40,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,9; 29,57</t>
+          <t>-50,56; 70,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,45; -4,31</t>
+          <t>-58,63; -6,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-64,63; -17,33</t>
+          <t>-65,52; -19,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 57,74</t>
+          <t>-13,18; 53,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-63,24; -18,62</t>
+          <t>-62,03; -20,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,87; -17,66</t>
+          <t>-60,94; -16,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,56; 28,58</t>
+          <t>-12,91; 49,31</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -2,1</t>
+          <t>-7,56; -2,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -0,98</t>
+          <t>-6,7; -1,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,02</t>
+          <t>-2,1; 4,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 2,98</t>
+          <t>-6,95; 2,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,32; -1,22</t>
+          <t>-10,23; -1,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 2,11</t>
+          <t>-5,87; 2,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -0,44</t>
+          <t>-5,86; -0,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -1,73</t>
+          <t>-7,3; -2,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 2,27</t>
+          <t>-2,98; 2,1</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-11,7%</t>
+          <t>-10,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-4,14%</t>
+          <t>-3,36%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-93,52; -42,17</t>
+          <t>-94,51; -44,65</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-83,18; -13,74</t>
+          <t>-83,8; -9,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 99,37</t>
+          <t>-26,97; 100,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 23,08</t>
+          <t>-39,0; 22,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-58,02; -8,63</t>
+          <t>-57,32; -10,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-32,45; 18,2</t>
+          <t>-32,36; 20,4</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-51,33; -5,28</t>
+          <t>-49,41; -5,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-60,45; -19,31</t>
+          <t>-60,9; -22,09</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 25,72</t>
+          <t>-24,08; 22,42</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-12,02</t>
+          <t>-6,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-6,42</t>
+          <t>-3,99</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,38; -0,29</t>
+          <t>-7,07; -0,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 0,13</t>
+          <t>-6,89; 0,13</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,65</t>
+          <t>-4,3; 2,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,4; -0,69</t>
+          <t>-12,1; -0,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,48; -2,1</t>
+          <t>-13,55; -2,78</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,52; -5,25</t>
+          <t>-11,34; -1,93</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-9,01; -1,89</t>
+          <t>-8,95; -2,03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,56; -2,4</t>
+          <t>-9,58; -2,47</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -2,88</t>
+          <t>-7,04; -0,98</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-9,92%</t>
+          <t>-8,23%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-53,87%</t>
+          <t>-29,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-42,62%</t>
+          <t>-26,53%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-82,89; 1,16</t>
+          <t>-81,68; -4,99</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-79,08; 10,11</t>
+          <t>-79,74; 4,13</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,11; 60,42</t>
+          <t>-47,41; 56,39</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-48,18; -2,44</t>
+          <t>-48,38; -3,88</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,92; -9,26</t>
+          <t>-54,07; -13,72</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-79,79; -24,43</t>
+          <t>-44,92; -10,74</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-51,94; -13,19</t>
+          <t>-52,68; -14,74</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-56,83; -17,66</t>
+          <t>-56,65; -18,26</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-73,77; -21,68</t>
+          <t>-41,32; -7,66</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -1,87</t>
+          <t>-10,57; -1,75</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 0,03</t>
+          <t>-9,51; -0,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 4,39</t>
+          <t>-5,01; 4,05</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 6,44</t>
+          <t>-6,78; 6,46</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-15,89; -2,58</t>
+          <t>-15,53; -2,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 4,38</t>
+          <t>-7,85; 4,24</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 2,37</t>
+          <t>-6,92; 2,11</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -3,13</t>
+          <t>-11,94; -3,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 2,91</t>
+          <t>-5,16; 2,69</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-1,72%</t>
+          <t>-0,31%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-6,27%</t>
+          <t>-5,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-6,47%</t>
+          <t>-5,79%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-86,73; -17,57</t>
+          <t>-86,46; -21,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-77,91; 8,41</t>
+          <t>-77,6; -0,92</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-42,78; 74,99</t>
+          <t>-42,05; 67,74</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 30,1</t>
+          <t>-23,61; 30,53</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-55,44; -11,3</t>
+          <t>-55,73; -12,45</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 19,79</t>
+          <t>-25,36; 20,5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 15,33</t>
+          <t>-31,94; 13,92</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-57,17; -18,14</t>
+          <t>-55,6; -16,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 18,21</t>
+          <t>-23,65; 17,26</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -1,15</t>
+          <t>-2,59; -1,06</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,26; -0,78</t>
+          <t>-2,23; -0,76</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,4</t>
+          <t>-0,08; 1,64</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,93</t>
+          <t>-3,76; -1,06</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -3,19</t>
+          <t>-6,07; -3,31</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,67</t>
+          <t>-1,22; 1,54</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -1,25</t>
+          <t>-2,84; -1,27</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -2,34</t>
+          <t>-3,86; -2,26</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,86</t>
+          <t>-0,36; 1,4</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-7,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-1,45%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-73,17; -40,89</t>
+          <t>-73,59; -41,53</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-65,38; -30,11</t>
+          <t>-64,25; -28,07</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 53,62</t>
+          <t>-2,19; 63,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-32,04; -9,15</t>
+          <t>-32,33; -10,1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-52,16; -31,78</t>
+          <t>-52,62; -32,44</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 6,52</t>
+          <t>-10,55; 15,49</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-40,05; -18,9</t>
+          <t>-39,02; -19,61</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-51,73; -34,87</t>
+          <t>-51,78; -34,24</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 13,3</t>
+          <t>-4,72; 22,54</t>
         </is>
       </c>
     </row>
